--- a/results/Synthetic Dataset 1/Synthetic Dataset 1 AUROC.xlsx
+++ b/results/Synthetic Dataset 1/Synthetic Dataset 1 AUROC.xlsx
@@ -1,14 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18611" windowHeight="8292"/>
+    <workbookView windowWidth="19164" windowHeight="13128"/>
   </bookViews>
   <sheets>
     <sheet name="model_1_detailed_results" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">model_1_detailed_results!$A$1:$C$149</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="5">
   <si>
     <t>Fold</t>
   </si>
@@ -36,6 +39,12 @@
   </si>
   <si>
     <t>Pred Score</t>
+  </si>
+  <si>
+    <t>GroupA</t>
+  </si>
+  <si>
+    <t>GroupB</t>
   </si>
 </sst>
 </file>
@@ -930,6 +939,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1206,8 +1222,8 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
       <c r="C2">
         <v>0.36619434</v>
@@ -1217,8 +1233,8 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>3</v>
       </c>
       <c r="C3">
         <v>0.44070852</v>
@@ -1228,8 +1244,8 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
       <c r="C4">
         <v>0.48139897</v>
@@ -1239,8 +1255,8 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
       <c r="C5">
         <v>0.344626</v>
@@ -1250,8 +1266,8 @@
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6">
-        <v>0</v>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
       <c r="C6">
         <v>0.42210868</v>
@@ -1261,8 +1277,8 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7">
-        <v>0</v>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
       <c r="C7">
         <v>0.4052206</v>
@@ -1272,8 +1288,8 @@
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8">
-        <v>0</v>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
       <c r="C8">
         <v>0.4276889</v>
@@ -1283,8 +1299,8 @@
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9">
-        <v>0</v>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
       <c r="C9">
         <v>0.37640876</v>
@@ -1294,8 +1310,8 @@
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10">
-        <v>0</v>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
       <c r="C10">
         <v>0.31059664</v>
@@ -1305,8 +1321,8 @@
       <c r="A11">
         <v>1</v>
       </c>
-      <c r="B11">
-        <v>0</v>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
       <c r="C11">
         <v>0.40821683</v>
@@ -1316,8 +1332,8 @@
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12">
-        <v>0</v>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
       <c r="C12">
         <v>0.4203108</v>
@@ -1327,8 +1343,8 @@
       <c r="A13">
         <v>1</v>
       </c>
-      <c r="B13">
-        <v>0</v>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
       <c r="C13">
         <v>0.32249284</v>
@@ -1338,8 +1354,8 @@
       <c r="A14">
         <v>1</v>
       </c>
-      <c r="B14">
-        <v>0</v>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
       <c r="C14">
         <v>0.3516799</v>
@@ -1349,8 +1365,8 @@
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15">
-        <v>0</v>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
       <c r="C15">
         <v>0.5615398</v>
@@ -1360,8 +1376,8 @@
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16">
-        <v>0</v>
+      <c r="B16" t="s">
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0.31853232</v>
@@ -1371,8 +1387,8 @@
       <c r="A17">
         <v>1</v>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="s">
+        <v>3</v>
       </c>
       <c r="C17">
         <v>0.35810748</v>
@@ -1382,8 +1398,8 @@
       <c r="A18">
         <v>1</v>
       </c>
-      <c r="B18">
-        <v>1</v>
+      <c r="B18" t="s">
+        <v>4</v>
       </c>
       <c r="C18">
         <v>0.54537714</v>
@@ -1393,8 +1409,8 @@
       <c r="A19">
         <v>1</v>
       </c>
-      <c r="B19">
-        <v>1</v>
+      <c r="B19" t="s">
+        <v>4</v>
       </c>
       <c r="C19">
         <v>0.61787295</v>
@@ -1404,8 +1420,8 @@
       <c r="A20">
         <v>1</v>
       </c>
-      <c r="B20">
-        <v>1</v>
+      <c r="B20" t="s">
+        <v>4</v>
       </c>
       <c r="C20">
         <v>0.555727</v>
@@ -1415,8 +1431,8 @@
       <c r="A21">
         <v>1</v>
       </c>
-      <c r="B21">
-        <v>1</v>
+      <c r="B21" t="s">
+        <v>4</v>
       </c>
       <c r="C21">
         <v>0.65342724</v>
@@ -1426,8 +1442,8 @@
       <c r="A22">
         <v>1</v>
       </c>
-      <c r="B22">
-        <v>1</v>
+      <c r="B22" t="s">
+        <v>4</v>
       </c>
       <c r="C22">
         <v>0.43678227</v>
@@ -1437,8 +1453,8 @@
       <c r="A23">
         <v>1</v>
       </c>
-      <c r="B23">
-        <v>1</v>
+      <c r="B23" t="s">
+        <v>4</v>
       </c>
       <c r="C23">
         <v>0.60220975</v>
@@ -1448,8 +1464,8 @@
       <c r="A24">
         <v>1</v>
       </c>
-      <c r="B24">
-        <v>1</v>
+      <c r="B24" t="s">
+        <v>4</v>
       </c>
       <c r="C24">
         <v>0.732859</v>
@@ -1459,8 +1475,8 @@
       <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25">
-        <v>1</v>
+      <c r="B25" t="s">
+        <v>4</v>
       </c>
       <c r="C25">
         <v>0.53037035</v>
@@ -1470,8 +1486,8 @@
       <c r="A26">
         <v>1</v>
       </c>
-      <c r="B26">
-        <v>1</v>
+      <c r="B26" t="s">
+        <v>4</v>
       </c>
       <c r="C26">
         <v>0.58831805</v>
@@ -1481,8 +1497,8 @@
       <c r="A27">
         <v>1</v>
       </c>
-      <c r="B27">
-        <v>1</v>
+      <c r="B27" t="s">
+        <v>4</v>
       </c>
       <c r="C27">
         <v>0.52245873</v>
@@ -1492,8 +1508,8 @@
       <c r="A28">
         <v>1</v>
       </c>
-      <c r="B28">
-        <v>1</v>
+      <c r="B28" t="s">
+        <v>4</v>
       </c>
       <c r="C28">
         <v>0.47988096</v>
@@ -1503,8 +1519,8 @@
       <c r="A29">
         <v>1</v>
       </c>
-      <c r="B29">
-        <v>1</v>
+      <c r="B29" t="s">
+        <v>4</v>
       </c>
       <c r="C29">
         <v>0.45755264</v>
@@ -1514,8 +1530,8 @@
       <c r="A30">
         <v>1</v>
       </c>
-      <c r="B30">
-        <v>1</v>
+      <c r="B30" t="s">
+        <v>4</v>
       </c>
       <c r="C30">
         <v>0.57007533</v>
@@ -1525,8 +1541,8 @@
       <c r="A31">
         <v>1</v>
       </c>
-      <c r="B31">
-        <v>1</v>
+      <c r="B31" t="s">
+        <v>4</v>
       </c>
       <c r="C31">
         <v>0.57154846</v>
@@ -1536,8 +1552,8 @@
       <c r="A32">
         <v>2</v>
       </c>
-      <c r="B32">
-        <v>0</v>
+      <c r="B32" t="s">
+        <v>3</v>
       </c>
       <c r="C32">
         <v>0.36089414</v>
@@ -1547,8 +1563,8 @@
       <c r="A33">
         <v>2</v>
       </c>
-      <c r="B33">
-        <v>0</v>
+      <c r="B33" t="s">
+        <v>3</v>
       </c>
       <c r="C33">
         <v>0.30984548</v>
@@ -1558,8 +1574,8 @@
       <c r="A34">
         <v>2</v>
       </c>
-      <c r="B34">
-        <v>0</v>
+      <c r="B34" t="s">
+        <v>3</v>
       </c>
       <c r="C34">
         <v>0.40741596</v>
@@ -1569,8 +1585,8 @@
       <c r="A35">
         <v>2</v>
       </c>
-      <c r="B35">
-        <v>0</v>
+      <c r="B35" t="s">
+        <v>3</v>
       </c>
       <c r="C35">
         <v>0.5040514</v>
@@ -1580,8 +1596,8 @@
       <c r="A36">
         <v>2</v>
       </c>
-      <c r="B36">
-        <v>0</v>
+      <c r="B36" t="s">
+        <v>3</v>
       </c>
       <c r="C36">
         <v>0.34177876</v>
@@ -1591,8 +1607,8 @@
       <c r="A37">
         <v>2</v>
       </c>
-      <c r="B37">
-        <v>0</v>
+      <c r="B37" t="s">
+        <v>3</v>
       </c>
       <c r="C37">
         <v>0.2654671</v>
@@ -1602,8 +1618,8 @@
       <c r="A38">
         <v>2</v>
       </c>
-      <c r="B38">
-        <v>0</v>
+      <c r="B38" t="s">
+        <v>3</v>
       </c>
       <c r="C38">
         <v>0.44741213</v>
@@ -1613,8 +1629,8 @@
       <c r="A39">
         <v>2</v>
       </c>
-      <c r="B39">
-        <v>0</v>
+      <c r="B39" t="s">
+        <v>3</v>
       </c>
       <c r="C39">
         <v>0.41766876</v>
@@ -1624,8 +1640,8 @@
       <c r="A40">
         <v>2</v>
       </c>
-      <c r="B40">
-        <v>0</v>
+      <c r="B40" t="s">
+        <v>3</v>
       </c>
       <c r="C40">
         <v>0.41011465</v>
@@ -1635,8 +1651,8 @@
       <c r="A41">
         <v>2</v>
       </c>
-      <c r="B41">
-        <v>0</v>
+      <c r="B41" t="s">
+        <v>3</v>
       </c>
       <c r="C41">
         <v>0.32728407</v>
@@ -1646,8 +1662,8 @@
       <c r="A42">
         <v>2</v>
       </c>
-      <c r="B42">
-        <v>0</v>
+      <c r="B42" t="s">
+        <v>3</v>
       </c>
       <c r="C42">
         <v>0.345928</v>
@@ -1657,8 +1673,8 @@
       <c r="A43">
         <v>2</v>
       </c>
-      <c r="B43">
-        <v>0</v>
+      <c r="B43" t="s">
+        <v>3</v>
       </c>
       <c r="C43">
         <v>0.34771523</v>
@@ -1668,8 +1684,8 @@
       <c r="A44">
         <v>2</v>
       </c>
-      <c r="B44">
-        <v>0</v>
+      <c r="B44" t="s">
+        <v>3</v>
       </c>
       <c r="C44">
         <v>0.4168559</v>
@@ -1679,8 +1695,8 @@
       <c r="A45">
         <v>2</v>
       </c>
-      <c r="B45">
-        <v>0</v>
+      <c r="B45" t="s">
+        <v>3</v>
       </c>
       <c r="C45">
         <v>0.45271978</v>
@@ -1690,8 +1706,8 @@
       <c r="A46">
         <v>2</v>
       </c>
-      <c r="B46">
-        <v>0</v>
+      <c r="B46" t="s">
+        <v>3</v>
       </c>
       <c r="C46">
         <v>0.42478517</v>
@@ -1701,8 +1717,8 @@
       <c r="A47">
         <v>2</v>
       </c>
-      <c r="B47">
-        <v>0</v>
+      <c r="B47" t="s">
+        <v>3</v>
       </c>
       <c r="C47">
         <v>0.405604</v>
@@ -1712,8 +1728,8 @@
       <c r="A48">
         <v>2</v>
       </c>
-      <c r="B48">
-        <v>1</v>
+      <c r="B48" t="s">
+        <v>4</v>
       </c>
       <c r="C48">
         <v>0.56413573</v>
@@ -1723,8 +1739,8 @@
       <c r="A49">
         <v>2</v>
       </c>
-      <c r="B49">
-        <v>1</v>
+      <c r="B49" t="s">
+        <v>4</v>
       </c>
       <c r="C49">
         <v>0.5640849</v>
@@ -1734,8 +1750,8 @@
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="B50">
-        <v>1</v>
+      <c r="B50" t="s">
+        <v>4</v>
       </c>
       <c r="C50">
         <v>0.5562443</v>
@@ -1745,8 +1761,8 @@
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51">
-        <v>1</v>
+      <c r="B51" t="s">
+        <v>4</v>
       </c>
       <c r="C51">
         <v>0.6584181</v>
@@ -1756,8 +1772,8 @@
       <c r="A52">
         <v>2</v>
       </c>
-      <c r="B52">
-        <v>1</v>
+      <c r="B52" t="s">
+        <v>4</v>
       </c>
       <c r="C52">
         <v>0.7315011</v>
@@ -1767,8 +1783,8 @@
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53">
-        <v>1</v>
+      <c r="B53" t="s">
+        <v>4</v>
       </c>
       <c r="C53">
         <v>0.749964</v>
@@ -1778,8 +1794,8 @@
       <c r="A54">
         <v>2</v>
       </c>
-      <c r="B54">
-        <v>1</v>
+      <c r="B54" t="s">
+        <v>4</v>
       </c>
       <c r="C54">
         <v>0.6428848</v>
@@ -1789,8 +1805,8 @@
       <c r="A55">
         <v>2</v>
       </c>
-      <c r="B55">
-        <v>1</v>
+      <c r="B55" t="s">
+        <v>4</v>
       </c>
       <c r="C55">
         <v>0.7140941</v>
@@ -1800,8 +1816,8 @@
       <c r="A56">
         <v>2</v>
       </c>
-      <c r="B56">
-        <v>1</v>
+      <c r="B56" t="s">
+        <v>4</v>
       </c>
       <c r="C56">
         <v>0.5617058</v>
@@ -1811,8 +1827,8 @@
       <c r="A57">
         <v>2</v>
       </c>
-      <c r="B57">
-        <v>1</v>
+      <c r="B57" t="s">
+        <v>4</v>
       </c>
       <c r="C57">
         <v>0.5517759</v>
@@ -1822,8 +1838,8 @@
       <c r="A58">
         <v>2</v>
       </c>
-      <c r="B58">
-        <v>1</v>
+      <c r="B58" t="s">
+        <v>4</v>
       </c>
       <c r="C58">
         <v>0.6253648</v>
@@ -1833,8 +1849,8 @@
       <c r="A59">
         <v>2</v>
       </c>
-      <c r="B59">
-        <v>1</v>
+      <c r="B59" t="s">
+        <v>4</v>
       </c>
       <c r="C59">
         <v>0.5094573</v>
@@ -1844,8 +1860,8 @@
       <c r="A60">
         <v>2</v>
       </c>
-      <c r="B60">
-        <v>1</v>
+      <c r="B60" t="s">
+        <v>4</v>
       </c>
       <c r="C60">
         <v>0.60063905</v>
@@ -1855,8 +1871,8 @@
       <c r="A61">
         <v>2</v>
       </c>
-      <c r="B61">
-        <v>1</v>
+      <c r="B61" t="s">
+        <v>4</v>
       </c>
       <c r="C61">
         <v>0.50786424</v>
@@ -1866,8 +1882,8 @@
       <c r="A62">
         <v>3</v>
       </c>
-      <c r="B62">
-        <v>0</v>
+      <c r="B62" t="s">
+        <v>3</v>
       </c>
       <c r="C62">
         <v>0.47561255</v>
@@ -1877,8 +1893,8 @@
       <c r="A63">
         <v>3</v>
       </c>
-      <c r="B63">
-        <v>0</v>
+      <c r="B63" t="s">
+        <v>3</v>
       </c>
       <c r="C63">
         <v>0.31117666</v>
@@ -1888,8 +1904,8 @@
       <c r="A64">
         <v>3</v>
       </c>
-      <c r="B64">
-        <v>0</v>
+      <c r="B64" t="s">
+        <v>3</v>
       </c>
       <c r="C64">
         <v>0.39241108</v>
@@ -1899,8 +1915,8 @@
       <c r="A65">
         <v>3</v>
       </c>
-      <c r="B65">
-        <v>0</v>
+      <c r="B65" t="s">
+        <v>3</v>
       </c>
       <c r="C65">
         <v>0.45816094</v>
@@ -1910,8 +1926,8 @@
       <c r="A66">
         <v>3</v>
       </c>
-      <c r="B66">
-        <v>0</v>
+      <c r="B66" t="s">
+        <v>3</v>
       </c>
       <c r="C66">
         <v>0.44080475</v>
@@ -1921,8 +1937,8 @@
       <c r="A67">
         <v>3</v>
       </c>
-      <c r="B67">
-        <v>0</v>
+      <c r="B67" t="s">
+        <v>3</v>
       </c>
       <c r="C67">
         <v>0.3477478</v>
@@ -1932,8 +1948,8 @@
       <c r="A68">
         <v>3</v>
       </c>
-      <c r="B68">
-        <v>0</v>
+      <c r="B68" t="s">
+        <v>3</v>
       </c>
       <c r="C68">
         <v>0.36454186</v>
@@ -1943,8 +1959,8 @@
       <c r="A69">
         <v>3</v>
       </c>
-      <c r="B69">
-        <v>0</v>
+      <c r="B69" t="s">
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0.38884708</v>
@@ -1954,8 +1970,8 @@
       <c r="A70">
         <v>3</v>
       </c>
-      <c r="B70">
-        <v>0</v>
+      <c r="B70" t="s">
+        <v>3</v>
       </c>
       <c r="C70">
         <v>0.40217075</v>
@@ -1965,8 +1981,8 @@
       <c r="A71">
         <v>3</v>
       </c>
-      <c r="B71">
-        <v>0</v>
+      <c r="B71" t="s">
+        <v>3</v>
       </c>
       <c r="C71">
         <v>0.42050892</v>
@@ -1976,8 +1992,8 @@
       <c r="A72">
         <v>3</v>
       </c>
-      <c r="B72">
-        <v>0</v>
+      <c r="B72" t="s">
+        <v>3</v>
       </c>
       <c r="C72">
         <v>0.40691957</v>
@@ -1987,8 +2003,8 @@
       <c r="A73">
         <v>3</v>
       </c>
-      <c r="B73">
-        <v>0</v>
+      <c r="B73" t="s">
+        <v>3</v>
       </c>
       <c r="C73">
         <v>0.29213986</v>
@@ -1998,8 +2014,8 @@
       <c r="A74">
         <v>3</v>
       </c>
-      <c r="B74">
-        <v>0</v>
+      <c r="B74" t="s">
+        <v>3</v>
       </c>
       <c r="C74">
         <v>0.4741685</v>
@@ -2009,8 +2025,8 @@
       <c r="A75">
         <v>3</v>
       </c>
-      <c r="B75">
-        <v>0</v>
+      <c r="B75" t="s">
+        <v>3</v>
       </c>
       <c r="C75">
         <v>0.36747795</v>
@@ -2020,8 +2036,8 @@
       <c r="A76">
         <v>3</v>
       </c>
-      <c r="B76">
-        <v>0</v>
+      <c r="B76" t="s">
+        <v>3</v>
       </c>
       <c r="C76">
         <v>0.3539315</v>
@@ -2031,8 +2047,8 @@
       <c r="A77">
         <v>3</v>
       </c>
-      <c r="B77">
-        <v>1</v>
+      <c r="B77" t="s">
+        <v>4</v>
       </c>
       <c r="C77">
         <v>0.65087205</v>
@@ -2042,8 +2058,8 @@
       <c r="A78">
         <v>3</v>
       </c>
-      <c r="B78">
-        <v>1</v>
+      <c r="B78" t="s">
+        <v>4</v>
       </c>
       <c r="C78">
         <v>0.574931</v>
@@ -2053,8 +2069,8 @@
       <c r="A79">
         <v>3</v>
       </c>
-      <c r="B79">
-        <v>1</v>
+      <c r="B79" t="s">
+        <v>4</v>
       </c>
       <c r="C79">
         <v>0.61951536</v>
@@ -2064,8 +2080,8 @@
       <c r="A80">
         <v>3</v>
       </c>
-      <c r="B80">
-        <v>1</v>
+      <c r="B80" t="s">
+        <v>4</v>
       </c>
       <c r="C80">
         <v>0.7108442</v>
@@ -2075,8 +2091,8 @@
       <c r="A81">
         <v>3</v>
       </c>
-      <c r="B81">
-        <v>1</v>
+      <c r="B81" t="s">
+        <v>4</v>
       </c>
       <c r="C81">
         <v>0.6265257</v>
@@ -2086,8 +2102,8 @@
       <c r="A82">
         <v>3</v>
       </c>
-      <c r="B82">
-        <v>1</v>
+      <c r="B82" t="s">
+        <v>4</v>
       </c>
       <c r="C82">
         <v>0.48324892</v>
@@ -2097,8 +2113,8 @@
       <c r="A83">
         <v>3</v>
       </c>
-      <c r="B83">
-        <v>1</v>
+      <c r="B83" t="s">
+        <v>4</v>
       </c>
       <c r="C83">
         <v>0.77576303</v>
@@ -2108,8 +2124,8 @@
       <c r="A84">
         <v>3</v>
       </c>
-      <c r="B84">
-        <v>1</v>
+      <c r="B84" t="s">
+        <v>4</v>
       </c>
       <c r="C84">
         <v>0.66526663</v>
@@ -2119,8 +2135,8 @@
       <c r="A85">
         <v>3</v>
       </c>
-      <c r="B85">
-        <v>1</v>
+      <c r="B85" t="s">
+        <v>4</v>
       </c>
       <c r="C85">
         <v>0.74342567</v>
@@ -2130,8 +2146,8 @@
       <c r="A86">
         <v>3</v>
       </c>
-      <c r="B86">
-        <v>1</v>
+      <c r="B86" t="s">
+        <v>4</v>
       </c>
       <c r="C86">
         <v>0.5175184</v>
@@ -2141,8 +2157,8 @@
       <c r="A87">
         <v>3</v>
       </c>
-      <c r="B87">
-        <v>1</v>
+      <c r="B87" t="s">
+        <v>4</v>
       </c>
       <c r="C87">
         <v>0.5577913</v>
@@ -2152,8 +2168,8 @@
       <c r="A88">
         <v>3</v>
       </c>
-      <c r="B88">
-        <v>1</v>
+      <c r="B88" t="s">
+        <v>4</v>
       </c>
       <c r="C88">
         <v>0.48785442</v>
@@ -2163,8 +2179,8 @@
       <c r="A89">
         <v>3</v>
       </c>
-      <c r="B89">
-        <v>1</v>
+      <c r="B89" t="s">
+        <v>4</v>
       </c>
       <c r="C89">
         <v>0.47014245</v>
@@ -2174,8 +2190,8 @@
       <c r="A90">
         <v>3</v>
       </c>
-      <c r="B90">
-        <v>1</v>
+      <c r="B90" t="s">
+        <v>4</v>
       </c>
       <c r="C90">
         <v>0.56854165</v>
@@ -2185,8 +2201,8 @@
       <c r="A91">
         <v>3</v>
       </c>
-      <c r="B91">
-        <v>1</v>
+      <c r="B91" t="s">
+        <v>4</v>
       </c>
       <c r="C91">
         <v>0.5385355</v>
@@ -2196,8 +2212,8 @@
       <c r="A92">
         <v>4</v>
       </c>
-      <c r="B92">
-        <v>0</v>
+      <c r="B92" t="s">
+        <v>3</v>
       </c>
       <c r="C92">
         <v>0.4480265</v>
@@ -2207,8 +2223,8 @@
       <c r="A93">
         <v>4</v>
       </c>
-      <c r="B93">
-        <v>0</v>
+      <c r="B93" t="s">
+        <v>3</v>
       </c>
       <c r="C93">
         <v>0.44194075</v>
@@ -2218,8 +2234,8 @@
       <c r="A94">
         <v>4</v>
       </c>
-      <c r="B94">
-        <v>0</v>
+      <c r="B94" t="s">
+        <v>3</v>
       </c>
       <c r="C94">
         <v>0.44486523</v>
@@ -2229,8 +2245,8 @@
       <c r="A95">
         <v>4</v>
       </c>
-      <c r="B95">
-        <v>0</v>
+      <c r="B95" t="s">
+        <v>3</v>
       </c>
       <c r="C95">
         <v>0.42017832</v>
@@ -2240,8 +2256,8 @@
       <c r="A96">
         <v>4</v>
       </c>
-      <c r="B96">
-        <v>0</v>
+      <c r="B96" t="s">
+        <v>3</v>
       </c>
       <c r="C96">
         <v>0.35987514</v>
@@ -2251,8 +2267,8 @@
       <c r="A97">
         <v>4</v>
       </c>
-      <c r="B97">
-        <v>0</v>
+      <c r="B97" t="s">
+        <v>3</v>
       </c>
       <c r="C97">
         <v>0.45350808</v>
@@ -2262,8 +2278,8 @@
       <c r="A98">
         <v>4</v>
       </c>
-      <c r="B98">
-        <v>0</v>
+      <c r="B98" t="s">
+        <v>3</v>
       </c>
       <c r="C98">
         <v>0.37806806</v>
@@ -2273,8 +2289,8 @@
       <c r="A99">
         <v>4</v>
       </c>
-      <c r="B99">
-        <v>0</v>
+      <c r="B99" t="s">
+        <v>3</v>
       </c>
       <c r="C99">
         <v>0.42737862</v>
@@ -2284,8 +2300,8 @@
       <c r="A100">
         <v>4</v>
       </c>
-      <c r="B100">
-        <v>0</v>
+      <c r="B100" t="s">
+        <v>3</v>
       </c>
       <c r="C100">
         <v>0.60766286</v>
@@ -2295,8 +2311,8 @@
       <c r="A101">
         <v>4</v>
       </c>
-      <c r="B101">
-        <v>0</v>
+      <c r="B101" t="s">
+        <v>3</v>
       </c>
       <c r="C101">
         <v>0.4742292</v>
@@ -2306,8 +2322,8 @@
       <c r="A102">
         <v>4</v>
       </c>
-      <c r="B102">
-        <v>0</v>
+      <c r="B102" t="s">
+        <v>3</v>
       </c>
       <c r="C102">
         <v>0.44155034</v>
@@ -2317,8 +2333,8 @@
       <c r="A103">
         <v>4</v>
       </c>
-      <c r="B103">
-        <v>0</v>
+      <c r="B103" t="s">
+        <v>3</v>
       </c>
       <c r="C103">
         <v>0.34575948</v>
@@ -2328,8 +2344,8 @@
       <c r="A104">
         <v>4</v>
       </c>
-      <c r="B104">
-        <v>0</v>
+      <c r="B104" t="s">
+        <v>3</v>
       </c>
       <c r="C104">
         <v>0.5072511</v>
@@ -2339,8 +2355,8 @@
       <c r="A105">
         <v>4</v>
       </c>
-      <c r="B105">
-        <v>0</v>
+      <c r="B105" t="s">
+        <v>3</v>
       </c>
       <c r="C105">
         <v>0.48633558</v>
@@ -2350,8 +2366,8 @@
       <c r="A106">
         <v>4</v>
       </c>
-      <c r="B106">
-        <v>0</v>
+      <c r="B106" t="s">
+        <v>3</v>
       </c>
       <c r="C106">
         <v>0.42987975</v>
@@ -2361,8 +2377,8 @@
       <c r="A107">
         <v>4</v>
       </c>
-      <c r="B107">
-        <v>1</v>
+      <c r="B107" t="s">
+        <v>4</v>
       </c>
       <c r="C107">
         <v>0.47419354</v>
@@ -2372,8 +2388,8 @@
       <c r="A108">
         <v>4</v>
       </c>
-      <c r="B108">
-        <v>1</v>
+      <c r="B108" t="s">
+        <v>4</v>
       </c>
       <c r="C108">
         <v>0.75275195</v>
@@ -2383,8 +2399,8 @@
       <c r="A109">
         <v>4</v>
       </c>
-      <c r="B109">
-        <v>1</v>
+      <c r="B109" t="s">
+        <v>4</v>
       </c>
       <c r="C109">
         <v>0.7433143</v>
@@ -2394,8 +2410,8 @@
       <c r="A110">
         <v>4</v>
       </c>
-      <c r="B110">
-        <v>1</v>
+      <c r="B110" t="s">
+        <v>4</v>
       </c>
       <c r="C110">
         <v>0.6343807</v>
@@ -2405,8 +2421,8 @@
       <c r="A111">
         <v>4</v>
       </c>
-      <c r="B111">
-        <v>1</v>
+      <c r="B111" t="s">
+        <v>4</v>
       </c>
       <c r="C111">
         <v>0.57807475</v>
@@ -2416,8 +2432,8 @@
       <c r="A112">
         <v>4</v>
       </c>
-      <c r="B112">
-        <v>1</v>
+      <c r="B112" t="s">
+        <v>4</v>
       </c>
       <c r="C112">
         <v>0.83165896</v>
@@ -2427,8 +2443,8 @@
       <c r="A113">
         <v>4</v>
       </c>
-      <c r="B113">
-        <v>1</v>
+      <c r="B113" t="s">
+        <v>4</v>
       </c>
       <c r="C113">
         <v>0.6604835</v>
@@ -2438,8 +2454,8 @@
       <c r="A114">
         <v>4</v>
       </c>
-      <c r="B114">
-        <v>1</v>
+      <c r="B114" t="s">
+        <v>4</v>
       </c>
       <c r="C114">
         <v>0.5617355</v>
@@ -2449,8 +2465,8 @@
       <c r="A115">
         <v>4</v>
       </c>
-      <c r="B115">
-        <v>1</v>
+      <c r="B115" t="s">
+        <v>4</v>
       </c>
       <c r="C115">
         <v>0.70043814</v>
@@ -2460,8 +2476,8 @@
       <c r="A116">
         <v>4</v>
       </c>
-      <c r="B116">
-        <v>1</v>
+      <c r="B116" t="s">
+        <v>4</v>
       </c>
       <c r="C116">
         <v>0.54125017</v>
@@ -2471,8 +2487,8 @@
       <c r="A117">
         <v>4</v>
       </c>
-      <c r="B117">
-        <v>1</v>
+      <c r="B117" t="s">
+        <v>4</v>
       </c>
       <c r="C117">
         <v>0.6427214</v>
@@ -2482,8 +2498,8 @@
       <c r="A118">
         <v>4</v>
       </c>
-      <c r="B118">
-        <v>1</v>
+      <c r="B118" t="s">
+        <v>4</v>
       </c>
       <c r="C118">
         <v>0.40316767</v>
@@ -2493,8 +2509,8 @@
       <c r="A119">
         <v>4</v>
       </c>
-      <c r="B119">
-        <v>1</v>
+      <c r="B119" t="s">
+        <v>4</v>
       </c>
       <c r="C119">
         <v>0.79141605</v>
@@ -2504,8 +2520,8 @@
       <c r="A120">
         <v>4</v>
       </c>
-      <c r="B120">
-        <v>1</v>
+      <c r="B120" t="s">
+        <v>4</v>
       </c>
       <c r="C120">
         <v>0.6660479</v>
@@ -2515,8 +2531,8 @@
       <c r="A121">
         <v>5</v>
       </c>
-      <c r="B121">
-        <v>0</v>
+      <c r="B121" t="s">
+        <v>3</v>
       </c>
       <c r="C121">
         <v>0.43288454</v>
@@ -2526,8 +2542,8 @@
       <c r="A122">
         <v>5</v>
       </c>
-      <c r="B122">
-        <v>0</v>
+      <c r="B122" t="s">
+        <v>3</v>
       </c>
       <c r="C122">
         <v>0.3796583</v>
@@ -2537,8 +2553,8 @@
       <c r="A123">
         <v>5</v>
       </c>
-      <c r="B123">
-        <v>0</v>
+      <c r="B123" t="s">
+        <v>3</v>
       </c>
       <c r="C123">
         <v>0.3638609</v>
@@ -2548,8 +2564,8 @@
       <c r="A124">
         <v>5</v>
       </c>
-      <c r="B124">
-        <v>0</v>
+      <c r="B124" t="s">
+        <v>3</v>
       </c>
       <c r="C124">
         <v>0.46852905</v>
@@ -2559,8 +2575,8 @@
       <c r="A125">
         <v>5</v>
       </c>
-      <c r="B125">
-        <v>0</v>
+      <c r="B125" t="s">
+        <v>3</v>
       </c>
       <c r="C125">
         <v>0.31325856</v>
@@ -2570,8 +2586,8 @@
       <c r="A126">
         <v>5</v>
       </c>
-      <c r="B126">
-        <v>0</v>
+      <c r="B126" t="s">
+        <v>3</v>
       </c>
       <c r="C126">
         <v>0.403995</v>
@@ -2581,8 +2597,8 @@
       <c r="A127">
         <v>5</v>
       </c>
-      <c r="B127">
-        <v>0</v>
+      <c r="B127" t="s">
+        <v>3</v>
       </c>
       <c r="C127">
         <v>0.5137454</v>
@@ -2592,8 +2608,8 @@
       <c r="A128">
         <v>5</v>
       </c>
-      <c r="B128">
-        <v>0</v>
+      <c r="B128" t="s">
+        <v>3</v>
       </c>
       <c r="C128">
         <v>0.36888546</v>
@@ -2603,8 +2619,8 @@
       <c r="A129">
         <v>5</v>
       </c>
-      <c r="B129">
-        <v>0</v>
+      <c r="B129" t="s">
+        <v>3</v>
       </c>
       <c r="C129">
         <v>0.3061885</v>
@@ -2614,8 +2630,8 @@
       <c r="A130">
         <v>5</v>
       </c>
-      <c r="B130">
-        <v>0</v>
+      <c r="B130" t="s">
+        <v>3</v>
       </c>
       <c r="C130">
         <v>0.5796115</v>
@@ -2625,8 +2641,8 @@
       <c r="A131">
         <v>5</v>
       </c>
-      <c r="B131">
-        <v>0</v>
+      <c r="B131" t="s">
+        <v>3</v>
       </c>
       <c r="C131">
         <v>0.36811483</v>
@@ -2636,8 +2652,8 @@
       <c r="A132">
         <v>5</v>
       </c>
-      <c r="B132">
-        <v>0</v>
+      <c r="B132" t="s">
+        <v>3</v>
       </c>
       <c r="C132">
         <v>0.2909934</v>
@@ -2647,8 +2663,8 @@
       <c r="A133">
         <v>5</v>
       </c>
-      <c r="B133">
-        <v>0</v>
+      <c r="B133" t="s">
+        <v>3</v>
       </c>
       <c r="C133">
         <v>0.35585397</v>
@@ -2658,8 +2674,8 @@
       <c r="A134">
         <v>5</v>
       </c>
-      <c r="B134">
-        <v>0</v>
+      <c r="B134" t="s">
+        <v>3</v>
       </c>
       <c r="C134">
         <v>0.34308273</v>
@@ -2669,8 +2685,8 @@
       <c r="A135">
         <v>5</v>
       </c>
-      <c r="B135">
-        <v>0</v>
+      <c r="B135" t="s">
+        <v>3</v>
       </c>
       <c r="C135">
         <v>0.49227557</v>
@@ -2680,8 +2696,8 @@
       <c r="A136">
         <v>5</v>
       </c>
-      <c r="B136">
-        <v>1</v>
+      <c r="B136" t="s">
+        <v>4</v>
       </c>
       <c r="C136">
         <v>0.6166798</v>
@@ -2691,8 +2707,8 @@
       <c r="A137">
         <v>5</v>
       </c>
-      <c r="B137">
-        <v>1</v>
+      <c r="B137" t="s">
+        <v>4</v>
       </c>
       <c r="C137">
         <v>0.7901144</v>
@@ -2702,8 +2718,8 @@
       <c r="A138">
         <v>5</v>
       </c>
-      <c r="B138">
-        <v>1</v>
+      <c r="B138" t="s">
+        <v>4</v>
       </c>
       <c r="C138">
         <v>0.3779353</v>
@@ -2713,8 +2729,8 @@
       <c r="A139">
         <v>5</v>
       </c>
-      <c r="B139">
-        <v>1</v>
+      <c r="B139" t="s">
+        <v>4</v>
       </c>
       <c r="C139">
         <v>0.56623125</v>
@@ -2724,8 +2740,8 @@
       <c r="A140">
         <v>5</v>
       </c>
-      <c r="B140">
-        <v>1</v>
+      <c r="B140" t="s">
+        <v>4</v>
       </c>
       <c r="C140">
         <v>0.8064837</v>
@@ -2735,8 +2751,8 @@
       <c r="A141">
         <v>5</v>
       </c>
-      <c r="B141">
-        <v>1</v>
+      <c r="B141" t="s">
+        <v>4</v>
       </c>
       <c r="C141">
         <v>0.80041945</v>
@@ -2746,8 +2762,8 @@
       <c r="A142">
         <v>5</v>
       </c>
-      <c r="B142">
-        <v>1</v>
+      <c r="B142" t="s">
+        <v>4</v>
       </c>
       <c r="C142">
         <v>0.5206884</v>
@@ -2757,8 +2773,8 @@
       <c r="A143">
         <v>5</v>
       </c>
-      <c r="B143">
-        <v>1</v>
+      <c r="B143" t="s">
+        <v>4</v>
       </c>
       <c r="C143">
         <v>0.73204476</v>
@@ -2768,8 +2784,8 @@
       <c r="A144">
         <v>5</v>
       </c>
-      <c r="B144">
-        <v>1</v>
+      <c r="B144" t="s">
+        <v>4</v>
       </c>
       <c r="C144">
         <v>0.49546903</v>
@@ -2779,8 +2795,8 @@
       <c r="A145">
         <v>5</v>
       </c>
-      <c r="B145">
-        <v>1</v>
+      <c r="B145" t="s">
+        <v>4</v>
       </c>
       <c r="C145">
         <v>0.67159903</v>
@@ -2790,8 +2806,8 @@
       <c r="A146">
         <v>5</v>
       </c>
-      <c r="B146">
-        <v>1</v>
+      <c r="B146" t="s">
+        <v>4</v>
       </c>
       <c r="C146">
         <v>0.4280447</v>
@@ -2801,8 +2817,8 @@
       <c r="A147">
         <v>5</v>
       </c>
-      <c r="B147">
-        <v>1</v>
+      <c r="B147" t="s">
+        <v>4</v>
       </c>
       <c r="C147">
         <v>0.38537988</v>
@@ -2812,8 +2828,8 @@
       <c r="A148">
         <v>5</v>
       </c>
-      <c r="B148">
-        <v>1</v>
+      <c r="B148" t="s">
+        <v>4</v>
       </c>
       <c r="C148">
         <v>0.5790139</v>
@@ -2823,14 +2839,17 @@
       <c r="A149">
         <v>5</v>
       </c>
-      <c r="B149">
-        <v>1</v>
+      <c r="B149" t="s">
+        <v>4</v>
       </c>
       <c r="C149">
         <v>0.67267746</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C149" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
